--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/EIXO SELETOR.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/EIXO SELETOR.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,7 +472,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -503,7 +492,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -524,11 +512,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -549,7 +532,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -570,7 +552,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -591,11 +572,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -616,11 +592,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -641,9 +612,124 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>60</t>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>7899468089503</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EIXO SELETOR CAMBIO MHX POP110I 2016 A 2021</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>7899468089510</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EIXO SELETOR CAMBIO MHX POP100 2007 A 2015</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>7908305601645</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EIXO SELETOR CAMBIO MHX TWISTER250/ TORNADO250/ XRE300/ CB300R</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>751320984449</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EIXO SELETOR CAMBIO IRON  YBR125 2008/ XTZ125/ FACTOR125 182719</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>751320984425</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EIXO SELETOR CAMBIO IRON TITAN150/ FAN125 2009</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>751320984500</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EIXO CAMBIO IRON FAZER250 2018/ XTZ250 LANDER</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
